--- a/stories/arbres/ATOM-SEC.PAR.001-12.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-12.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Cécile arrive au jardin. Maman vient avec elle. Maman montre les cerceaux. C'est l'espace montré. Cécile saute dans un cerceau. Le cerceau est rouge. Il sent le plastique chaud. Maman s'assoit sur le banc. L'adulte voit Cécile. Cécile reste dans l'espace montré. Maman dit : je te vois. L'adulte voit. Cécile saute encore. Ses pieds tapent l'herbe. Elle reste là où maman a dit. Maman sourit. Cécile range un cerceau. Elle reste près. L'espace montré, c'est ici. L'adulte voit.</t>
+          <t>Cécile arrive au jardin. Maman vient avec elle. Maman montre les cerceaux. C'est l'espace montré. Cécile saute dans un cerceau. Le cerceau est rouge. Il sent le plastique chaud. Maman s'assoit sur le banc. L'adulte voit Cécile. Cécile reste dans l'espace montré. Je te vois. L'adulte voit. Cécile saute encore. Ses pieds tapent l'herbe. Elle reste là où maman a dit. Maman sourit. Cécile range un cerceau. Elle reste près. L'espace montré, c'est ici. L'adulte voit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Cécile arrive au jardin. Maman vient avec elle. Maman montre les cerceaux. C'est l'espace montré. Cécile saute dans un cerceau. Le cerceau est rouge. Il sent le plastique chaud. Maman s'assoit sur le banc. L'adulte voit Cécile. Cécile reste dans l'espace montré.
+maman|Je te vois. L'adulte voit.
+narrateur|Cécile saute encore. Ses pieds tapent l'herbe. Elle reste là où maman a dit. Maman sourit. Cécile range un cerceau. Elle reste près. L'espace montré, c'est ici. L'adulte voit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1488,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Cécile joue au jardin. Où reste-t-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1661,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Cécile est restée dans l'espace montré. Aux cerceaux. L'adulte voit.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1828,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Cécile prend la main de maman. Elles quittent le jardin.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1995,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-12.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-12.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,7 @@
 narrateur|Cécile saute encore. Ses pieds tapent l'herbe. Elle reste là où maman a dit. Maman sourit. Cécile range un cerceau. Elle reste près. L'espace montré, c'est ici. L'adulte voit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1495,6 +1501,7 @@
           <t>narrateur|Cécile joue au jardin. Où reste-t-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1666,6 +1673,7 @@
           <t>narrateur|Cécile est restée dans l'espace montré. Aux cerceaux. L'adulte voit.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1841,7 @@
           <t>narrateur|Cécile prend la main de maman. Elles quittent le jardin.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2052,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2267,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.PAR.001-12.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-12.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cécile joue où maman voit</t>
+          <t>Les cerceaux de Mila</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mila saute dans les cerceaux du jardin, dans l'espace que maman a montré.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Cécile arrive au jardin. Maman vient avec elle. Maman montre les cerceaux. C'est l'espace montré. Cécile saute dans un cerceau. Le cerceau est rouge. Il sent le plastique chaud. Maman s'assoit sur le banc. L'adulte voit Cécile. Cécile reste dans l'espace montré. Je te vois. L'adulte voit. Cécile saute encore. Ses pieds tapent l'herbe. Elle reste là où maman a dit. Maman sourit. Cécile range un cerceau. Elle reste près. L'espace montré, c'est ici. L'adulte voit.</t>
+          <t>Un cerceau rouge chauffe dans l'herbe. Le jardin sent les fleurs. Le plastique est chaud au soleil. Une fourmi croise une tige. Le banc de bois est clair. Maman vient avec Mila. Tu as vu le cerceau, Mila ? Oui, maman. Il est rouge. En ce moment, maman montre les cerceaux. C'est l'espace montré. Tu joues ici. L'adulte voit. Ici ? Oui. Dans l'espace montré. Mila saute dans un cerceau. Le cerceau est rouge. Il sent le plastique chaud. Maman s'assoit sur le banc. L'adulte voit Mila. Mila reste dans l'espace montré. Je te vois. L'adulte voit. Tu me vois ? Oui. Mila saute encore. Ses pieds tapent l'herbe. L'herbe est un peu piquante. Elle reste là où maman a dit. Encore un saut. Oui. Dans l'espace montré. Tu restes dans l'espace montré ? Oui. Ici. Bravo, Mila. Tu as fait du bon travail. Mila range un cerceau. Le plastique claque, tout léger. Elle reste près. L'espace montré, c'est ici. L'adulte voit. Tu joues là où l'adulte a dit. Là où l'adulte a dit. Oui. Une fourmi reprend sa route. Mila saute dans le cerceau bleu. Elle reste dans l'espace montré. Tu as fini de sauter ? Encore un peu. Mila saute une dernière fois. Ses pieds sentent l'herbe chaude. Maman la voit. L'adulte voit. Le cerceau bleu est un peu plus frais. Mila le pose près du rouge. Rouge et bleu. Oui. Dans l'espace montré. Une fleur penche vers l'herbe. Mila la sent, tout près. Ça sent bon. Oui. Tu restes ici ? Oui. Bravo. Mila reste dans l'espace montré. L'adulte voit. Le soleil chauffe encore le cerceau rouge. Mila le touche du doigt. Il est chaud. Oui.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,9 +1324,79 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Cécile arrive au jardin. Maman vient avec elle. Maman montre les cerceaux. C'est l'espace montré. Cécile saute dans un cerceau. Le cerceau est rouge. Il sent le plastique chaud. Maman s'assoit sur le banc. L'adulte voit Cécile. Cécile reste dans l'espace montré.
-maman|Je te vois. L'adulte voit.
-narrateur|Cécile saute encore. Ses pieds tapent l'herbe. Elle reste là où maman a dit. Maman sourit. Cécile range un cerceau. Elle reste près. L'espace montré, c'est ici. L'adulte voit.</t>
+          <t>narrateur|Un cerceau rouge chauffe dans l'herbe.
+narrateur|Le jardin sent les fleurs.
+narrateur|Le plastique est chaud au soleil.
+narrateur|Une fourmi croise une tige.
+narrateur|Le banc de bois est clair.
+narrateur|Maman vient avec Mila.
+maman|Tu as vu le cerceau, Mila ?
+enfant-f|Oui, maman.
+enfant-f|Il est rouge.
+narrateur|En ce moment, maman montre les cerceaux.
+maman|C'est l'espace montré.
+maman|Tu joues ici.
+maman|L'adulte voit.
+enfant-f|Ici ?
+maman|Oui.
+maman|Dans l'espace montré.
+narrateur|Mila saute dans un cerceau.
+narrateur|Le cerceau est rouge.
+narrateur|Il sent le plastique chaud.
+narrateur|Maman s'assoit sur le banc.
+narrateur|L'adulte voit Mila.
+narrateur|Mila reste dans l'espace montré.
+maman|Je te vois.
+maman|L'adulte voit.
+enfant-f|Tu me vois ?
+maman|Oui.
+narrateur|Mila saute encore.
+narrateur|Ses pieds tapent l'herbe.
+narrateur|L'herbe est un peu piquante.
+narrateur|Elle reste là où maman a dit.
+enfant-f|Encore un saut.
+maman|Oui.
+maman|Dans l'espace montré.
+maman|Tu restes dans l'espace montré ?
+enfant-f|Oui.
+enfant-f|Ici.
+maman|Bravo, Mila.
+maman|Tu as fait du bon travail.
+narrateur|Mila range un cerceau.
+narrateur|Le plastique claque, tout léger.
+narrateur|Elle reste près.
+narrateur|L'espace montré, c'est ici.
+narrateur|L'adulte voit.
+maman|Tu joues là où l'adulte a dit.
+enfant-f|Là où l'adulte a dit.
+maman|Oui.
+narrateur|Une fourmi reprend sa route.
+narrateur|Mila saute dans le cerceau bleu.
+narrateur|Elle reste dans l'espace montré.
+maman|Tu as fini de sauter ?
+enfant-f|Encore un peu.
+narrateur|Mila saute une dernière fois.
+narrateur|Ses pieds sentent l'herbe chaude.
+narrateur|Maman la voit.
+narrateur|L'adulte voit.
+narrateur|Le cerceau bleu est un peu plus frais.
+narrateur|Mila le pose près du rouge.
+enfant-f|Rouge et bleu.
+maman|Oui.
+maman|Dans l'espace montré.
+narrateur|Une fleur penche vers l'herbe.
+narrateur|Mila la sent, tout près.
+enfant-f|Ça sent bon.
+maman|Oui.
+maman|Tu restes ici ?
+enfant-f|Oui.
+maman|Bravo.
+narrateur|Mila reste dans l'espace montré.
+narrateur|L'adulte voit.
+narrateur|Le soleil chauffe encore le cerceau rouge.
+narrateur|Mila le touche du doigt.
+enfant-f|Il est chaud.
+maman|Oui.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1342,7 +1424,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Cécile joue au jardin. Où reste-t-elle ?</t>
+          <t>Mila joue au jardin. Où reste-t-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1498,7 +1580,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Cécile joue au jardin. Où reste-t-elle ?</t>
+          <t>narrateur|Mila joue au jardin.
+narrateur|Où reste-t-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1526,7 +1609,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Cécile est restée dans l'espace montré. Aux cerceaux. L'adulte voit.</t>
+          <t>Mila est restée dans l'espace montré. Aux cerceaux. L'adulte voit. Tu es restée dans l'espace montré ? Oui. Bravo. L'adulte voit. Le cerceau rouge reste dans l'herbe.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1670,7 +1753,14 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Cécile est restée dans l'espace montré. Aux cerceaux. L'adulte voit.</t>
+          <t>narrateur|Mila est restée dans l'espace montré.
+narrateur|Aux cerceaux.
+narrateur|L'adulte voit.
+maman|Tu es restée dans l'espace montré ?
+enfant-f|Oui.
+maman|Bravo.
+maman|L'adulte voit.
+narrateur|Le cerceau rouge reste dans l'herbe.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1698,7 +1788,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Cécile prend la main de maman. Elles quittent le jardin.</t>
+          <t>Mila prend la main de maman. Tu as fini de ranger ? Oui, maman. Bravo. Elles quittent le jardin. L'herbe est encore chaude. Le cerceau rouge reste au soleil.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1838,7 +1928,13 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Cécile prend la main de maman. Elles quittent le jardin.</t>
+          <t>narrateur|Mila prend la main de maman.
+maman|Tu as fini de ranger ?
+enfant-f|Oui, maman.
+maman|Bravo.
+narrateur|Elles quittent le jardin.
+narrateur|L'herbe est encore chaude.
+narrateur|Le cerceau rouge reste au soleil.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1866,7 +1962,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila tient la main de maman. On a sauté. Oui. Dans l'espace montré. Bravo, Mila. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2006,7 +2102,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Mila tient la main de maman.
+enfant-f|On a sauté.
+maman|Oui.
+maman|Dans l'espace montré.
+maman|Bravo, Mila.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2028,7 +2129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2066,6 +2167,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-12.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-12.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un cerceau rouge chauffe dans l'herbe. Le jardin sent les fleurs. Le plastique est chaud au soleil. Une fourmi croise une tige. Le banc de bois est clair. Maman vient avec Mila. Tu as vu le cerceau, Mila ? Oui, maman. Il est rouge. En ce moment, maman montre les cerceaux. C'est l'espace montré. Tu joues ici. L'adulte voit. Ici ? Oui. Dans l'espace montré. Mila saute dans un cerceau. Le cerceau est rouge. Il sent le plastique chaud. Maman s'assoit sur le banc. L'adulte voit Mila. Mila reste dans l'espace montré. Je te vois. L'adulte voit. Tu me vois ? Oui. Mila saute encore. Ses pieds tapent l'herbe. L'herbe est un peu piquante. Elle reste là où maman a dit. Encore un saut. Oui. Dans l'espace montré. Tu restes dans l'espace montré ? Oui. Ici. Bravo, Mila. Tu as fait du bon travail. Mila range un cerceau. Le plastique claque, tout léger. Elle reste près. L'espace montré, c'est ici. L'adulte voit. Tu joues là où l'adulte a dit. Là où l'adulte a dit. Oui. Une fourmi reprend sa route. Mila saute dans le cerceau bleu. Elle reste dans l'espace montré. Tu as fini de sauter ? Encore un peu. Mila saute une dernière fois. Ses pieds sentent l'herbe chaude. Maman la voit. L'adulte voit. Le cerceau bleu est un peu plus frais. Mila le pose près du rouge. Rouge et bleu. Oui. Dans l'espace montré. Une fleur penche vers l'herbe. Mila la sent, tout près. Ça sent bon. Oui. Tu restes ici ? Oui. Bravo. Mila reste dans l'espace montré. L'adulte voit. Le soleil chauffe encore le cerceau rouge. Mila le touche du doigt. Il est chaud. Oui.</t>
+          <t>Un cerceau rouge chauffe dans l'herbe. Le jardin sent les fleurs. Le plastique est chaud au soleil. Une fourmi croise une tige. Le banc de bois est clair. Maman vient avec Mila. Tu as vu le cerceau, Mila ? Oui, maman. Il est rouge. En ce moment, maman montre les cerceaux. C'est l'espace montré. Tu joues ici. L'adulte voit. Ici ? Oui. Dans l'espace montré. Mila saute dans un cerceau. Le cerceau est rouge. Il sent le plastique chaud. Maman s'assoit sur le banc. L'adulte voit Mila. Mila reste dans l'espace montré. Je te vois. L'adulte voit. Tu me vois ? Oui. Mila saute encore. Ses pieds tapent l'herbe. L'herbe est un peu piquante. Elle reste là où maman a dit. Encore un saut. Oui. Dans l'espace montré. Tu restes dans l'espace montré ? Oui. Ici. Bravo, Mila. Mila range un cerceau. Le plastique claque, tout léger. Elle reste près. L'espace montré, c'est ici. L'adulte voit. Tu joues là où l'adulte a dit. Là où l'adulte a dit. Oui. Une fourmi reprend sa route. Mila saute dans le cerceau bleu. Elle reste dans l'espace montré. Tu as fini de sauter ? Encore un peu. Mila saute une dernière fois. Ses pieds sentent l'herbe chaude. Maman la voit. L'adulte voit. Le cerceau bleu est un peu plus frais. Mila le pose près du rouge. Rouge et bleu. Oui. Dans l'espace montré. Une fleur penche vers l'herbe. Mila la sent, tout près. Ça sent bon. Oui. Tu restes ici ? Oui. Bravo. Mila reste dans l'espace montré. L'adulte voit. Le soleil chauffe encore le cerceau rouge. Mila le touche du doigt. Il est chaud. Oui.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Cécile arrive au jardin. Maman vient avec elle. Maman montre les cerceaux. C'est l'&lt;emphasis level="moderate"&gt;espace&lt;/emphasis&gt; montré. Cécile saute dans un cerceau. Le cerceau est rouge. Il sent le plastique chaud. Maman s'assoit sur le banc. L'adulte voit Cécile. Cécile reste dans l'espace montré. Maman dit : je te vois. L'adulte voit. Cécile saute encore. Ses pieds tapent l'herbe. Elle reste là où maman a dit. Maman sourit. Cécile range un cerceau. Elle reste près. L'espace montré, c'est ici. L'adulte voit.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un cerceau rouge chauffe dans l'herbe. Le jardin sent les fleurs. Le plastique est chaud au soleil. Une fourmi croise une tige. Le banc de bois est clair. Maman vient avec Mila. Tu as vu le cerceau, Mila ? Oui, maman. Il est rouge. En ce moment, maman montre les cerceaux. C'est l'espace montré. Tu joues ici. L'adulte voit. Ici ? Oui. Dans l'espace montré. Mila saute dans un cerceau. Le cerceau est rouge. Il sent le plastique chaud. Maman s'assoit sur le banc. L'adulte voit Mila. Mila reste dans l'espace montré. Je te vois. L'adulte voit. Tu me vois ? Oui. Mila saute encore. Ses pieds tapent l'herbe. L'herbe est un peu piquante. Elle reste là où maman a dit. Encore un saut. Oui. Dans l'espace montré. Tu restes dans l'espace montré ? Oui. Ici. Bravo, Mila. Mila range un cerceau. Le plastique claque, tout léger. Elle reste près. L'espace montré, c'est ici. L'adulte voit. Tu joues là où l'adulte a dit. Là où l'adulte a dit. Oui. Une fourmi reprend sa route. Mila saute dans le cerceau bleu. Elle reste dans l'espace montré. Tu as fini de sauter ? Encore un peu. Mila saute une dernière fois. Ses pieds sentent l'herbe chaude. Maman la voit. L'adulte voit. Le cerceau bleu est un peu plus frais. Mila le pose près du rouge. Rouge et bleu. Oui. Dans l'espace montré. Une fleur penche vers l'herbe. Mila la sent, tout près. Ça sent bon. Oui. Tu restes ici ? Oui. Bravo. Mila reste dans l'espace montré. L'adulte voit. Le soleil chauffe encore le cerceau rouge. Mila le touche du doigt. Il est chaud. Oui.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1361,7 +1361,6 @@
 enfant-f|Oui.
 enfant-f|Ici.
 maman|Bravo, Mila.
-maman|Tu as fait du bon travail.
 narrateur|Mila range un cerceau.
 narrateur|Le plastique claque, tout léger.
 narrateur|Elle reste près.
@@ -1399,7 +1398,6 @@
 maman|Oui.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1429,7 +1427,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Cécile joue au jardin. Où reste-t-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila joue au jardin. Où reste-t-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1584,7 +1582,6 @@
 narrateur|Où reste-t-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1614,7 +1611,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Cécile est restée dans l'&lt;emphasis level="moderate"&gt;espace&lt;/emphasis&gt; montré. Aux cerceaux. L'adulte voit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila est restée dans l'espace montré. Aux cerceaux. L'adulte voit. Tu es restée dans l'espace montré ? Oui. Bravo. L'adulte voit. Le cerceau rouge reste dans l'herbe.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1763,7 +1760,6 @@
 narrateur|Le cerceau rouge reste dans l'herbe.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1793,7 +1789,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Cécile prend la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; de maman. Elles quittent le jardin.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila prend la main de maman. Tu as fini de ranger ? Oui, maman. Bravo. Elles quittent le jardin. L'herbe est encore chaude. Le cerceau rouge reste au soleil.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1937,7 +1933,6 @@
 narrateur|Le cerceau rouge reste au soleil.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1962,12 +1957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Mila tient la main de maman. On a sauté. Oui. Dans l'espace montré. Bravo, Mila. L'histoire est finie.</t>
+          <t>Mila tient la main de maman. On a sauté. Oui. Dans l'espace montré. Bravo, Mila.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila tient la main de maman. On a sauté. Oui. Dans l'espace montré. Bravo, Mila.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2106,11 +2101,9 @@
 enfant-f|On a sauté.
 maman|Oui.
 maman|Dans l'espace montré.
-maman|Bravo, Mila.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+maman|Bravo, Mila.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2129,7 +2122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2174,6 +2167,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-12.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-12.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cécile, maman</t>
+          <t>Mila, maman</t>
         </is>
       </c>
     </row>
